--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126119678</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126119487</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126119550</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126119727</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>126119824</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126119678</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126119550</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126119678</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126119550</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126119678</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126119487</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126119550</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126119727</v>
       </c>
       <c r="B5" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>126119824</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126119678</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126119550</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126119678</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126119487</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126119550</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126119727</v>
       </c>
       <c r="B5" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>126119824</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126119678</v>
+        <v>126119349</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Röstmyran, Röstmyran, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484191</v>
+        <v>484085</v>
       </c>
       <c r="R2" t="n">
-        <v>6843007</v>
+        <v>6842865</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -784,11 +775,11 @@
         <v>126119487</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126119550</v>
+        <v>126119824</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,43 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Röstmyran, Röstmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484194</v>
+        <v>484120</v>
       </c>
       <c r="R4" t="n">
-        <v>6842992</v>
+        <v>6842976</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,7 +969,7 @@
         <v>126119727</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126119824</v>
+        <v>126119471</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484120</v>
+        <v>484174</v>
       </c>
       <c r="R6" t="n">
-        <v>6842976</v>
+        <v>6842940</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,6 +1162,218 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126119550</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röstmyran, Röstmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484194</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6842992</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126119678</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röstmyran, Röstmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>484191</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6843007</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21474-2023 artfynd.xlsx
+++ b/artfynd/A 21474-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119727</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119471</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119550</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,8 +1409,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126119678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>